--- a/운영서식/1조_재료비 신청 목록_김진규_Mate.xlsx
+++ b/운영서식/1조_재료비 신청 목록_김진규_Mate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\LastProject\운영서식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C440BCC-683F-4105-8B79-2C780836D281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2B1C36-6E7D-4905-8744-621B860B5BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Col1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>품목명</t>
   </si>
@@ -160,10 +160,6 @@
   </si>
   <si>
     <t>USB 스피커</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raspberry Pi 5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -443,15 +439,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -465,6 +452,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -973,35 +969,33 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="17.399999999999999">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="24" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>1</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26">
         <v>3410</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="31"/>
-      <c r="B8" s="31"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="15.6">
-      <c r="A9" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9" s="10"/>
       <c r="B9" s="21"/>
       <c r="C9" s="7"/>
       <c r="D9" s="8"/>
@@ -1055,12 +1049,12 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="8">
         <f>SUM(E4:E14)</f>
         <v>187590</v>
